--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>154</v>
       </c>
       <c r="D2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>852</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D3">
         <v>738</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>852</v>
